--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N231_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N231_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.90107130669978</v>
+        <v>6.321424087338715</v>
       </c>
       <c r="D2" t="n">
-        <v>49.78409525561916</v>
+        <v>8.089915479038114</v>
       </c>
       <c r="E2" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F2" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.67296074830612</v>
+        <v>2.384356121599745</v>
       </c>
       <c r="D3" t="n">
-        <v>26.7479244084661</v>
+        <v>4.346537716375741</v>
       </c>
       <c r="E3" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F3" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.83054024470979</v>
+        <v>3.547462789765341</v>
       </c>
       <c r="D4" t="n">
-        <v>19.1157785111829</v>
+        <v>3.10631400806722</v>
       </c>
       <c r="E4" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F4" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.56475248907856</v>
+        <v>4.316772279475267</v>
       </c>
       <c r="D5" t="n">
-        <v>14.2783200614545</v>
+        <v>2.320227009986356</v>
       </c>
       <c r="E5" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F5" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.9433022352602</v>
+        <v>4.540786613229783</v>
       </c>
       <c r="D6" t="n">
-        <v>31.58882690006891</v>
+        <v>5.133184371261198</v>
       </c>
       <c r="E6" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F6" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.56313077386237</v>
+        <v>4.154008750752635</v>
       </c>
       <c r="D7" t="n">
-        <v>15.80573862365807</v>
+        <v>2.568432526344436</v>
       </c>
       <c r="E7" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F7" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.1722754031223</v>
+        <v>4.577994753007373</v>
       </c>
       <c r="D8" t="n">
-        <v>15.04976399196805</v>
+        <v>2.445586648694809</v>
       </c>
       <c r="E8" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F8" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.56768548079742</v>
+        <v>4.804748890629581</v>
       </c>
       <c r="D9" t="n">
-        <v>31.10296100734659</v>
+        <v>5.054231163693821</v>
       </c>
       <c r="E9" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F9" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.14198446367081</v>
+        <v>4.248072475346506</v>
       </c>
       <c r="D10" t="n">
-        <v>28.57770166365927</v>
+        <v>4.643876520344631</v>
       </c>
       <c r="E10" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F10" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.5859579413774</v>
+        <v>3.507718165473827</v>
       </c>
       <c r="D11" t="n">
-        <v>29.44514595020225</v>
+        <v>4.784836216907866</v>
       </c>
       <c r="E11" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F11" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.16800743027436</v>
+        <v>7.339801207419584</v>
       </c>
       <c r="D12" t="n">
-        <v>11.76981552776261</v>
+        <v>1.912595023261424</v>
       </c>
       <c r="E12" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F12" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.75659529185393</v>
+        <v>6.460446734926263</v>
       </c>
       <c r="D13" t="n">
-        <v>11.10089434071086</v>
+        <v>1.803895330365514</v>
       </c>
       <c r="E13" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F13" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>17.91931115549991</v>
+        <v>2.911888062768736</v>
       </c>
       <c r="D14" t="n">
-        <v>22.02271554554524</v>
+        <v>3.578691276151102</v>
       </c>
       <c r="E14" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F14" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.6485512216639</v>
+        <v>4.980389573520384</v>
       </c>
       <c r="D15" t="n">
-        <v>9.654244897625761</v>
+        <v>1.568814795864186</v>
       </c>
       <c r="E15" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F15" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.34281657956366</v>
+        <v>2.655707694179096</v>
       </c>
       <c r="D16" t="n">
-        <v>16.15076182221806</v>
+        <v>2.624498796110435</v>
       </c>
       <c r="E16" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F16" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>16.53159512722188</v>
+        <v>2.686384208173556</v>
       </c>
       <c r="D17" t="n">
-        <v>8.388135927277309</v>
+        <v>1.363072088182563</v>
       </c>
       <c r="E17" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F17" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>17.39731475671284</v>
+        <v>2.827063647965837</v>
       </c>
       <c r="D18" t="n">
-        <v>10.88695851579594</v>
+        <v>1.76913075881684</v>
       </c>
       <c r="E18" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F18" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>5.408326913195984</v>
+        <v>0.8788531233943475</v>
       </c>
       <c r="D19" t="n">
-        <v>9.655748084658182</v>
+        <v>1.569059063756955</v>
       </c>
       <c r="E19" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F19" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>10.30296283108016</v>
+        <v>1.674231460050526</v>
       </c>
       <c r="D20" t="n">
-        <v>5.615464959557503</v>
+        <v>0.9125130559280943</v>
       </c>
       <c r="E20" t="n">
-        <v>9.907214110352667</v>
+        <v>1.609922292932308</v>
       </c>
       <c r="F20" t="n">
-        <v>10.81915611444761</v>
+        <v>1.758112868597736</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
